--- a/Management/Goethe-Zertifikat C1 Scoring.xlsx
+++ b/Management/Goethe-Zertifikat C1 Scoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aciww-my.sharepoint.com/personal/daniel_lozanobarrero_aciworldwide_com/Documents/Documents/My-Notes/Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="11_F25DC773A252ABDACC104884B95956845ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13FA197E-087E-431B-B877-1AD3F50F587D}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="11_F25DC773A252ABDACC104884B95956845ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C29E7A0F-089F-4C4E-8B60-46238B0D3B77}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="14">
   <si>
     <t>LESEN</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Teil 4</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Max. Punkte</t>
   </si>
   <si>
@@ -79,13 +76,17 @@
   <si>
     <t>Vorges. Zeit</t>
   </si>
+  <si>
+    <t>Gesamt</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="[m]:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -104,15 +105,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -407,32 +420,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -454,50 +441,375 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dashed">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dashed">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dashed">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dashed">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dashed">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top style="dashed">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -507,98 +819,244 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="24">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -618,6 +1076,61 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FF63BE7B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF548235"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFA9D18E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFEB84"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4B183"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF8696B"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1088,698 +1601,1103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:O38"/>
+  <dimension ref="C1:T38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="93" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.88671875" style="78"/>
+    <col min="16" max="16" width="8.88671875" style="93"/>
+    <col min="17" max="17" width="8.88671875" style="78"/>
+    <col min="19" max="19" width="8.88671875" style="93"/>
+    <col min="20" max="20" width="8.88671875" style="78"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D3" s="16" t="s">
+    <row r="1" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="H1"/>
+      <c r="M1"/>
+      <c r="P1"/>
+      <c r="S1"/>
+    </row>
+    <row r="2" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="79"/>
+      <c r="H2"/>
+      <c r="M2"/>
+      <c r="P2"/>
+      <c r="S2"/>
+    </row>
+    <row r="3" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D3" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="16" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="16" t="s">
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="16" t="s">
+      <c r="O3" s="49"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="18"/>
-    </row>
-    <row r="4" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="13" t="s">
+      <c r="R3" s="49"/>
+      <c r="S3" s="50"/>
+      <c r="T3"/>
+    </row>
+    <row r="4" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="J4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="K4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="L4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="M4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="O4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="P4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="R4" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="S4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="T4"/>
+    </row>
+    <row r="5" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="7">
         <v>6</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="8">
         <v>6</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="8">
         <v>3</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="52">
         <v>7</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="55">
+        <f>IF(COUNTBLANK(D5:G5)&gt;0,"",SUM(D5:G5))</f>
+        <v>22</v>
+      </c>
+      <c r="I5" s="45">
         <v>5</v>
       </c>
-      <c r="I5" s="20">
+      <c r="J5" s="8">
         <v>7</v>
       </c>
-      <c r="J5" s="20">
+      <c r="K5" s="8">
         <v>8</v>
       </c>
-      <c r="K5" s="21">
+      <c r="L5" s="9">
         <v>6</v>
       </c>
-      <c r="L5" s="19">
+      <c r="M5" s="55">
+        <f>IF(COUNTBLANK(I5:L5)&gt;0,"",SUM(I5:L5))</f>
+        <v>26</v>
+      </c>
+      <c r="N5" s="7">
         <v>41</v>
       </c>
-      <c r="M5" s="21">
+      <c r="O5" s="9">
         <v>27.5</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="P5" s="55">
+        <f>IF(COUNTBLANK(N5:O5)&gt;0,"",SUM(N5:O5))</f>
+        <v>68.5</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="55" t="str">
+        <f>IF(COUNTBLANK(Q5:R5)&gt;0,"",SUM(Q5:R5))</f>
+        <v/>
+      </c>
+      <c r="T5"/>
+    </row>
+    <row r="6" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="10">
+        <v>5</v>
+      </c>
+      <c r="E6" s="11">
+        <v>4</v>
+      </c>
+      <c r="F6" s="11">
+        <v>3</v>
+      </c>
+      <c r="G6" s="53">
+        <v>4</v>
+      </c>
+      <c r="H6" s="55">
+        <f t="shared" ref="H6:H15" si="0">IF(COUNTBLANK(D6:G6)&gt;0,"",SUM(D6:G6))</f>
+        <v>16</v>
+      </c>
+      <c r="I6" s="46"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="56"/>
+      <c r="T6"/>
+    </row>
+    <row r="7" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I7" s="46"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="56"/>
+      <c r="T7"/>
+    </row>
+    <row r="8" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I8" s="46"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="56"/>
+      <c r="T8"/>
+    </row>
+    <row r="9" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I9" s="46"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="56"/>
+      <c r="T9"/>
+    </row>
+    <row r="10" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C10" s="2">
+        <v>6</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I10" s="46"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="56"/>
+      <c r="T10"/>
+    </row>
+    <row r="11" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C11" s="2">
+        <v>7</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I11" s="46"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="56"/>
+      <c r="T11"/>
+    </row>
+    <row r="12" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C12" s="2">
         <v>8</v>
       </c>
-      <c r="O5" s="21" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I12" s="46"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="56"/>
+      <c r="T12"/>
+    </row>
+    <row r="13" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C13" s="2">
+        <v>9</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I13" s="46"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="56"/>
+      <c r="T13"/>
+    </row>
+    <row r="14" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C14" s="2">
+        <v>10</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I14" s="46"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="56"/>
+      <c r="T14"/>
+    </row>
+    <row r="15" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="3">
+        <v>11</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I15" s="47"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="57"/>
+      <c r="T15"/>
+    </row>
+    <row r="16" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D16" s="76"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="76"/>
+      <c r="N16" s="76"/>
+      <c r="P16" s="78"/>
+      <c r="S16" s="78"/>
+    </row>
+    <row r="17" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="29" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C6" s="5">
+      <c r="D17" s="24">
+        <v>8</v>
+      </c>
+      <c r="E17" s="25">
+        <v>7</v>
+      </c>
+      <c r="F17" s="25">
+        <v>8</v>
+      </c>
+      <c r="G17" s="59">
+        <v>7</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="24">
+        <v>6</v>
+      </c>
+      <c r="J17" s="25">
+        <v>9</v>
+      </c>
+      <c r="K17" s="25">
+        <v>8</v>
+      </c>
+      <c r="L17" s="59">
+        <v>7</v>
+      </c>
+      <c r="M17" s="23">
+        <v>30</v>
+      </c>
+      <c r="N17" s="24">
+        <v>60</v>
+      </c>
+      <c r="O17" s="59">
+        <v>40</v>
+      </c>
+      <c r="P17" s="23">
+        <v>30</v>
+      </c>
+      <c r="Q17" s="24">
+        <v>52</v>
+      </c>
+      <c r="R17" s="26">
+        <v>32</v>
+      </c>
+      <c r="S17" s="58">
+        <v>30</v>
+      </c>
+      <c r="T17"/>
+    </row>
+    <row r="18" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="20"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="89"/>
+      <c r="N18" s="77"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="89"/>
+      <c r="Q18" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="R18" s="28"/>
+      <c r="S18" s="81"/>
+    </row>
+    <row r="19" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D19" s="79"/>
+      <c r="H19" s="78"/>
+      <c r="N19" s="79"/>
+      <c r="P19" s="78"/>
+      <c r="S19" s="78"/>
+    </row>
+    <row r="20" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D20" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="24"/>
-    </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C7" s="5">
-        <v>3</v>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="24"/>
-    </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C8" s="5">
+      <c r="O20" s="49"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="92"/>
+    </row>
+    <row r="21" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="24"/>
-    </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C9" s="5">
+      <c r="E21" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="24"/>
-    </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C10" s="5">
+      <c r="F21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="24"/>
-    </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C11" s="5">
+      <c r="G21" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="24"/>
-    </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C12" s="5">
-        <v>8</v>
-      </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="24"/>
-    </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C13" s="5">
-        <v>9</v>
-      </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="24"/>
-    </row>
-    <row r="14" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C14" s="5">
-        <v>10</v>
-      </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="24"/>
-    </row>
-    <row r="15" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="9">
-        <v>11</v>
-      </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="27"/>
-    </row>
-    <row r="16" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="34">
-        <v>8</v>
-      </c>
-      <c r="E17" s="35">
-        <v>7</v>
-      </c>
-      <c r="F17" s="35">
-        <v>8</v>
-      </c>
-      <c r="G17" s="35">
-        <v>7</v>
-      </c>
-      <c r="H17" s="35">
-        <v>6</v>
-      </c>
-      <c r="I17" s="35">
-        <v>9</v>
-      </c>
-      <c r="J17" s="35">
-        <v>8</v>
-      </c>
-      <c r="K17" s="35">
-        <v>7</v>
-      </c>
-      <c r="L17" s="35">
-        <v>60</v>
-      </c>
-      <c r="M17" s="35">
-        <v>40</v>
-      </c>
-      <c r="N17" s="36">
-        <v>52</v>
-      </c>
-      <c r="O17" s="37">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="O18" s="33"/>
-    </row>
-    <row r="19" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D20" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="I20" s="18"/>
-    </row>
-    <row r="21" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D21" s="13" t="s">
+      <c r="H21" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="81"/>
+      <c r="N21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="O21" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="P21" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q21"/>
+      <c r="S21" s="78"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C22" s="1">
         <v>1</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="30">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="E22" s="31">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="F22" s="31">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="G22" s="32">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="H22" s="63">
+        <f>IF(COUNTBLANK(D22:G22)&gt;0,"",SUM(D22:G22))</f>
+        <v>4.5138888888888888E-2</v>
+      </c>
+      <c r="I22" s="81"/>
+      <c r="N22" s="30">
+        <v>3.4722222222222224E-2</v>
+      </c>
+      <c r="O22" s="32">
+        <v>1.7361111111111112E-2</v>
+      </c>
+      <c r="P22" s="63">
+        <f>IF(COUNTBLANK(N22:O22)&gt;0,"",SUM(N22:O22))</f>
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="Q22"/>
+      <c r="S22" s="78"/>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="33">
+        <v>5.8333333333333336E-3</v>
+      </c>
+      <c r="E23" s="34">
+        <v>1.1921296296296296E-2</v>
+      </c>
+      <c r="F23" s="34">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="G23" s="35">
+        <v>9.6527777777777775E-3</v>
+      </c>
+      <c r="H23" s="63">
+        <f t="shared" ref="H23:H32" si="1">IF(COUNTBLANK(D23:G23)&gt;0,"",SUM(D23:G23))</f>
+        <v>4.1296296296296289E-2</v>
+      </c>
+      <c r="I23" s="81"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="63" t="str">
+        <f>IF(COUNTBLANK(N23:O23)&gt;0,"",SUM(N23:O23))</f>
+        <v/>
+      </c>
+      <c r="Q23"/>
+      <c r="S23" s="78"/>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="33"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I24" s="81"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="63" t="str">
+        <f t="shared" ref="P23:P32" si="2">IF(COUNTBLANK(N24:O24)&gt;0,"",SUM(N24:O24))</f>
+        <v/>
+      </c>
+      <c r="Q24"/>
+      <c r="S24" s="78"/>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I25" s="81"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="63" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q25"/>
+      <c r="S25" s="78"/>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C26" s="2">
+        <v>5</v>
+      </c>
+      <c r="D26" s="33"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I26" s="81"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="63" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q26"/>
+      <c r="S26" s="78"/>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C27" s="2">
+        <v>6</v>
+      </c>
+      <c r="D27" s="33"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="63" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q27"/>
+      <c r="S27" s="78"/>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C28" s="2">
+        <v>7</v>
+      </c>
+      <c r="D28" s="33"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="63" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q28"/>
+      <c r="S28" s="78"/>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C29" s="2">
+        <v>8</v>
+      </c>
+      <c r="D29" s="33"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="63" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q29"/>
+      <c r="S29" s="78"/>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C30" s="2">
+        <v>9</v>
+      </c>
+      <c r="D30" s="33"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I30" s="81"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="63" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q30"/>
+      <c r="S30" s="78"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C31" s="2">
         <v>10</v>
       </c>
-      <c r="E22" s="3">
-        <v>20</v>
-      </c>
-      <c r="F22" s="3">
-        <v>20</v>
-      </c>
-      <c r="G22" s="4">
-        <v>15</v>
-      </c>
-      <c r="H22" s="2">
-        <v>50</v>
-      </c>
-      <c r="I22" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C23" s="5">
-        <v>2</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C24" s="5">
+      <c r="D31" s="33"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I31" s="81"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="63" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q31"/>
+      <c r="S31" s="78"/>
+    </row>
+    <row r="32" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="3">
+        <v>11</v>
+      </c>
+      <c r="D32" s="36"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="64" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I32" s="84"/>
+      <c r="J32" s="85"/>
+      <c r="K32" s="85"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="91"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="64" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q32"/>
+      <c r="S32" s="78"/>
+    </row>
+    <row r="33" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D33" s="76"/>
+      <c r="H33" s="78"/>
+      <c r="N33" s="76"/>
+      <c r="P33" s="78"/>
+      <c r="Q33" s="86"/>
+      <c r="R33" s="83"/>
+      <c r="S33" s="92"/>
+    </row>
+    <row r="34" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C34" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="39">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="E34" s="40">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="F34" s="40">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="G34" s="60">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="H34" s="75">
+        <v>4.5138888888888888E-2</v>
+      </c>
+      <c r="I34" s="87"/>
+      <c r="J34" s="88"/>
+      <c r="K34" s="88"/>
+      <c r="L34" s="88"/>
+      <c r="M34" s="87"/>
+      <c r="N34" s="72">
+        <v>3.4722222222222224E-2</v>
+      </c>
+      <c r="O34" s="41">
+        <v>1.7361111111111112E-2</v>
+      </c>
+      <c r="P34" s="61">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="Q34" s="88"/>
+      <c r="R34" s="88"/>
+      <c r="S34" s="87"/>
+    </row>
+    <row r="35" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="D35" s="80"/>
+      <c r="H35" s="78"/>
+      <c r="N35" s="80"/>
+      <c r="P35" s="78"/>
+      <c r="S35" s="78"/>
+    </row>
+    <row r="36" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D36" s="79"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="79"/>
+      <c r="N36" s="79"/>
+      <c r="P36" s="78"/>
+      <c r="S36" s="78"/>
+    </row>
+    <row r="37" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="22">
+        <f>IFERROR(AVERAGE(D5:D15),"")</f>
+        <v>5.5</v>
+      </c>
+      <c r="E37" s="17">
+        <f t="shared" ref="E37:S37" si="3">IFERROR(AVERAGE(E5:E15),"")</f>
+        <v>5</v>
+      </c>
+      <c r="F37" s="17">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C25" s="5">
-        <v>4</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C26" s="5">
+      <c r="G37" s="65">
+        <f t="shared" si="3"/>
+        <v>5.5</v>
+      </c>
+      <c r="H37" s="67">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="I37" s="66">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C27" s="5">
+      <c r="J37" s="17">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="K37" s="17">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="L37" s="65">
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C28" s="5">
-        <v>7</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="8"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C29" s="5">
-        <v>8</v>
-      </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C30" s="5">
-        <v>9</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="8"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C31" s="5">
-        <v>10</v>
-      </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="8"/>
-    </row>
-    <row r="32" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="9">
+      <c r="M37" s="67">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="N37" s="66">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="O37" s="65">
+        <f t="shared" si="3"/>
+        <v>27.5</v>
+      </c>
+      <c r="P37" s="67">
+        <f t="shared" si="3"/>
+        <v>68.5</v>
+      </c>
+      <c r="Q37" s="66" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="R37" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S37" s="67" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="T37"/>
+    </row>
+    <row r="38" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C38" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="12"/>
-    </row>
-    <row r="33" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="34" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C34" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="34">
-        <v>10</v>
-      </c>
-      <c r="E34" s="35">
-        <v>20</v>
-      </c>
-      <c r="F34" s="35">
-        <v>20</v>
-      </c>
-      <c r="G34" s="35">
-        <v>15</v>
-      </c>
-      <c r="H34" s="35">
-        <v>50</v>
-      </c>
-      <c r="I34" s="44">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="37" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="43">
-        <f>IFERROR(AVERAGE(D5:D15),"")</f>
-        <v>6</v>
-      </c>
-      <c r="E37" s="29">
-        <f t="shared" ref="E37:O37" si="0">IFERROR(AVERAGE(E5:E15),"")</f>
-        <v>6</v>
-      </c>
-      <c r="F37" s="29">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G37" s="29">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="H37" s="29">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="I37" s="29">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="J37" s="29">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="K37" s="29">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="L37" s="29">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="M37" s="29">
-        <f t="shared" si="0"/>
-        <v>27.5</v>
-      </c>
-      <c r="N37" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O37" s="30" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C38" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="40">
+      <c r="D38" s="68">
         <f>IFERROR(AVERAGE(D22:D32),"")</f>
-        <v>10</v>
-      </c>
-      <c r="E38" s="41">
-        <f t="shared" ref="E38:M38" si="1">IFERROR(AVERAGE(E22:E32),"")</f>
-        <v>20</v>
-      </c>
-      <c r="F38" s="41">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="G38" s="41">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="H38" s="41">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="I38" s="42">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
+        <v>6.3888888888888884E-3</v>
+      </c>
+      <c r="E38" s="69">
+        <f t="shared" ref="E38:K38" si="4">IFERROR(AVERAGE(E22:E32),"")</f>
+        <v>1.2905092592592593E-2</v>
+      </c>
+      <c r="F38" s="70">
+        <f t="shared" si="4"/>
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="G38" s="71">
+        <f t="shared" si="4"/>
+        <v>1.0034722222222223E-2</v>
+      </c>
+      <c r="H38" s="71">
+        <f t="shared" si="4"/>
+        <v>4.3217592592592585E-2</v>
+      </c>
+      <c r="I38"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="94"/>
+      <c r="N38" s="73">
+        <f>IFERROR(AVERAGE(N22:N32),"")</f>
+        <v>3.4722222222222224E-2</v>
+      </c>
+      <c r="O38" s="74">
+        <f>IFERROR(AVERAGE(O22:O32),"")</f>
+        <v>1.7361111111111112E-2</v>
+      </c>
+      <c r="P38" s="71">
+        <f>IFERROR(AVERAGE(P22:P32),"")</f>
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="Q38"/>
+      <c r="S38" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="N20:P20"/>
   </mergeCells>
-  <conditionalFormatting sqref="D22:I32">
-    <cfRule type="expression" dxfId="18" priority="13">
+  <conditionalFormatting sqref="D22:H32 D38:H38 N22:P32">
+    <cfRule type="expression" dxfId="23" priority="35">
       <formula>AND(ISNUMBER(D22),D22&lt;=D$34)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D22:I32">
-    <cfRule type="expression" dxfId="17" priority="14">
+    <cfRule type="expression" dxfId="22" priority="36">
       <formula>AND(ISNUMBER(D22),D22&gt;D$34)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:O15">
-    <cfRule type="expression" dxfId="11" priority="15">
+  <conditionalFormatting sqref="D5:R15">
+    <cfRule type="expression" dxfId="21" priority="37">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&lt;=20%)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:O15">
-    <cfRule type="expression" dxfId="10" priority="16">
+    <cfRule type="expression" dxfId="20" priority="38">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&gt;20%,D5/D$17&lt;=40%)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:O15">
-    <cfRule type="expression" dxfId="9" priority="17">
+    <cfRule type="expression" dxfId="19" priority="39">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&gt;40%,D5/D$17&lt;=60%)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:O15">
-    <cfRule type="expression" dxfId="8" priority="18">
+    <cfRule type="expression" dxfId="18" priority="40">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&gt;60%,D5/D$17&lt;=80%)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:O15">
-    <cfRule type="expression" dxfId="7" priority="19">
+    <cfRule type="expression" dxfId="17" priority="41">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&gt;80%)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D37:O37">
-    <cfRule type="expression" dxfId="6" priority="20">
+  <conditionalFormatting sqref="D37:S37">
+    <cfRule type="expression" dxfId="16" priority="42">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&lt;=20%)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D37:O37">
-    <cfRule type="expression" dxfId="5" priority="21">
+    <cfRule type="expression" dxfId="15" priority="43">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&gt;20%,D37/D$17&lt;=40%)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D37:O37">
-    <cfRule type="expression" dxfId="4" priority="22">
+    <cfRule type="expression" dxfId="14" priority="44">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&gt;40%,D37/D$17&lt;=60%)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D37:O37">
-    <cfRule type="expression" dxfId="3" priority="23">
+    <cfRule type="expression" dxfId="13" priority="45">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&gt;60%,D37/D$17&lt;=80%)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D37:O37">
-    <cfRule type="expression" dxfId="2" priority="24">
+    <cfRule type="expression" dxfId="12" priority="46">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&gt;80%)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D38:I38">
-    <cfRule type="expression" dxfId="1" priority="25">
-      <formula>AND(ISNUMBER(D38),D38&lt;=D$34)</formula>
+  <conditionalFormatting sqref="S6:S15">
+    <cfRule type="expression" dxfId="11" priority="18">
+      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&lt;=20%)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="19">
+      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&gt;20%,S6/S$17&lt;=40%)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="20">
+      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&gt;40%,S6/S$17&lt;=60%)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="21">
+      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&gt;60%,S6/S$17&lt;=80%)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="22">
+      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&gt;80%)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D38:I38">
-    <cfRule type="expression" dxfId="0" priority="26">
-      <formula>AND(ISNUMBER(D38),D38&gt;D$34)</formula>
+  <conditionalFormatting sqref="S5">
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&lt;=20%)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&gt;20%,S5/S$17&lt;=40%)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="10">
+      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&gt;40%,S5/S$17&lt;=60%)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="11">
+      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&gt;60%,S5/S$17&lt;=80%)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="12">
+      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&gt;80%)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N38:P38">
+    <cfRule type="expression" dxfId="1" priority="55">
+      <formula>AND(ISNUMBER(N38),N38&lt;=N$34)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="56">
+      <formula>AND(ISNUMBER(N38),N38&gt;N$34)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Management/Goethe-Zertifikat C1 Scoring.xlsx
+++ b/Management/Goethe-Zertifikat C1 Scoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aciww-my.sharepoint.com/personal/daniel_lozanobarrero_aciworldwide_com/Documents/Documents/My-Notes/Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="11_F25DC773A252ABDACC104884B95956845ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C29E7A0F-089F-4C4E-8B60-46238B0D3B77}"/>
+  <xr:revisionPtr revIDLastSave="325" documentId="11_F25DC773A252ABDACC104884B95956845ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0598CF3B-46EF-4978-9DDF-AA604E0589D5}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,7 +86,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="[m]:ss"/>
+    <numFmt numFmtId="165" formatCode="[m]:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -125,7 +125,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -792,6 +792,54 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -861,12 +909,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -879,49 +921,43 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -942,15 +978,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -978,19 +1005,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1002,28 +1029,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
@@ -1033,7 +1048,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
@@ -1052,11 +1066,47 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="14">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1076,116 +1126,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FF63BE7B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF548235"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFA9D18E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB84"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF4B183"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF8696B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF548235"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFA9D18E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB84"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF4B183"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF8696B"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1605,16 +1545,16 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="67" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="93" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="81" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="67" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.88671875" style="78"/>
-    <col min="16" max="16" width="8.88671875" style="93"/>
-    <col min="17" max="17" width="8.88671875" style="78"/>
-    <col min="19" max="19" width="8.88671875" style="93"/>
-    <col min="20" max="20" width="8.88671875" style="78"/>
+    <col min="13" max="14" width="8.88671875" style="67"/>
+    <col min="16" max="16" width="8.88671875" style="81"/>
+    <col min="17" max="17" width="8.88671875" style="67"/>
+    <col min="19" max="19" width="8.88671875" style="81"/>
+    <col min="20" max="20" width="8.88671875" style="67"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:20" x14ac:dyDescent="0.3">
@@ -1624,37 +1564,37 @@
       <c r="S1"/>
     </row>
     <row r="2" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D2" s="79"/>
+      <c r="D2" s="68"/>
       <c r="H2"/>
       <c r="M2"/>
       <c r="P2"/>
       <c r="S2"/>
     </row>
     <row r="3" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="48" t="s">
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="48" t="s">
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="48" t="s">
+      <c r="O3" s="87"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="R3" s="49"/>
-      <c r="S3" s="50"/>
+      <c r="R3" s="87"/>
+      <c r="S3" s="88"/>
       <c r="T3"/>
     </row>
     <row r="4" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1667,13 +1607,13 @@
       <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="44" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="40" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="5" t="s">
@@ -1685,7 +1625,7 @@
       <c r="L4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="N4" s="4" t="s">
@@ -1721,14 +1661,14 @@
       <c r="F5" s="8">
         <v>3</v>
       </c>
-      <c r="G5" s="52">
+      <c r="G5" s="45">
         <v>7</v>
       </c>
-      <c r="H5" s="55">
+      <c r="H5" s="48">
         <f>IF(COUNTBLANK(D5:G5)&gt;0,"",SUM(D5:G5))</f>
         <v>22</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="41">
         <v>5</v>
       </c>
       <c r="J5" s="8">
@@ -1740,7 +1680,7 @@
       <c r="L5" s="9">
         <v>6</v>
       </c>
-      <c r="M5" s="55">
+      <c r="M5" s="48">
         <f>IF(COUNTBLANK(I5:L5)&gt;0,"",SUM(I5:L5))</f>
         <v>26</v>
       </c>
@@ -1750,13 +1690,13 @@
       <c r="O5" s="9">
         <v>27.5</v>
       </c>
-      <c r="P5" s="55">
+      <c r="P5" s="48">
         <f>IF(COUNTBLANK(N5:O5)&gt;0,"",SUM(N5:O5))</f>
         <v>68.5</v>
       </c>
       <c r="Q5" s="7"/>
       <c r="R5" s="9"/>
-      <c r="S5" s="55" t="str">
+      <c r="S5" s="48" t="str">
         <f>IF(COUNTBLANK(Q5:R5)&gt;0,"",SUM(Q5:R5))</f>
         <v/>
       </c>
@@ -1775,24 +1715,37 @@
       <c r="F6" s="11">
         <v>3</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="46">
         <v>4</v>
       </c>
-      <c r="H6" s="55">
+      <c r="H6" s="48">
         <f t="shared" ref="H6:H15" si="0">IF(COUNTBLANK(D6:G6)&gt;0,"",SUM(D6:G6))</f>
         <v>16</v>
       </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="10"/>
+      <c r="I6" s="42">
+        <v>5</v>
+      </c>
+      <c r="J6" s="11">
+        <v>6</v>
+      </c>
+      <c r="K6" s="11">
+        <v>5</v>
+      </c>
+      <c r="L6" s="12">
+        <v>6</v>
+      </c>
+      <c r="M6" s="48">
+        <f t="shared" ref="M6:M15" si="1">IF(COUNTBLANK(I6:L6)&gt;0,"",SUM(I6:L6))</f>
+        <v>22</v>
+      </c>
+      <c r="N6" s="10">
+        <v>38</v>
+      </c>
       <c r="O6" s="12"/>
-      <c r="P6" s="42"/>
+      <c r="P6" s="38"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="12"/>
-      <c r="S6" s="56"/>
+      <c r="S6" s="49"/>
       <c r="T6"/>
     </row>
     <row r="7" spans="3:20" x14ac:dyDescent="0.3">
@@ -1802,22 +1755,25 @@
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="55" t="str">
+      <c r="G7" s="46"/>
+      <c r="H7" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I7" s="46"/>
+      <c r="I7" s="42"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
-      <c r="M7" s="42"/>
+      <c r="M7" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="N7" s="10"/>
       <c r="O7" s="12"/>
-      <c r="P7" s="42"/>
+      <c r="P7" s="38"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="12"/>
-      <c r="S7" s="56"/>
+      <c r="S7" s="49"/>
       <c r="T7"/>
     </row>
     <row r="8" spans="3:20" x14ac:dyDescent="0.3">
@@ -1827,22 +1783,25 @@
       <c r="D8" s="10"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="55" t="str">
+      <c r="G8" s="46"/>
+      <c r="H8" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I8" s="46"/>
+      <c r="I8" s="42"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="42"/>
+      <c r="M8" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="N8" s="10"/>
       <c r="O8" s="12"/>
-      <c r="P8" s="42"/>
+      <c r="P8" s="38"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="12"/>
-      <c r="S8" s="56"/>
+      <c r="S8" s="49"/>
       <c r="T8"/>
     </row>
     <row r="9" spans="3:20" x14ac:dyDescent="0.3">
@@ -1852,22 +1811,25 @@
       <c r="D9" s="10"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="55" t="str">
+      <c r="G9" s="46"/>
+      <c r="H9" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I9" s="46"/>
+      <c r="I9" s="42"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="12"/>
-      <c r="M9" s="42"/>
+      <c r="M9" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="N9" s="10"/>
       <c r="O9" s="12"/>
-      <c r="P9" s="42"/>
+      <c r="P9" s="38"/>
       <c r="Q9" s="10"/>
       <c r="R9" s="12"/>
-      <c r="S9" s="56"/>
+      <c r="S9" s="49"/>
       <c r="T9"/>
     </row>
     <row r="10" spans="3:20" x14ac:dyDescent="0.3">
@@ -1877,22 +1839,25 @@
       <c r="D10" s="10"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="55" t="str">
+      <c r="G10" s="46"/>
+      <c r="H10" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I10" s="46"/>
+      <c r="I10" s="42"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
       <c r="L10" s="12"/>
-      <c r="M10" s="42"/>
+      <c r="M10" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="N10" s="10"/>
       <c r="O10" s="12"/>
-      <c r="P10" s="42"/>
+      <c r="P10" s="38"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="12"/>
-      <c r="S10" s="56"/>
+      <c r="S10" s="49"/>
       <c r="T10"/>
     </row>
     <row r="11" spans="3:20" x14ac:dyDescent="0.3">
@@ -1902,22 +1867,25 @@
       <c r="D11" s="10"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="55" t="str">
+      <c r="G11" s="46"/>
+      <c r="H11" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I11" s="46"/>
+      <c r="I11" s="42"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
       <c r="L11" s="12"/>
-      <c r="M11" s="42"/>
+      <c r="M11" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="N11" s="10"/>
       <c r="O11" s="12"/>
-      <c r="P11" s="42"/>
+      <c r="P11" s="38"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="12"/>
-      <c r="S11" s="56"/>
+      <c r="S11" s="49"/>
       <c r="T11"/>
     </row>
     <row r="12" spans="3:20" x14ac:dyDescent="0.3">
@@ -1927,22 +1895,25 @@
       <c r="D12" s="10"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="55" t="str">
+      <c r="G12" s="46"/>
+      <c r="H12" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I12" s="46"/>
+      <c r="I12" s="42"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="12"/>
-      <c r="M12" s="42"/>
+      <c r="M12" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="N12" s="10"/>
       <c r="O12" s="12"/>
-      <c r="P12" s="42"/>
+      <c r="P12" s="38"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="12"/>
-      <c r="S12" s="56"/>
+      <c r="S12" s="49"/>
       <c r="T12"/>
     </row>
     <row r="13" spans="3:20" x14ac:dyDescent="0.3">
@@ -1952,22 +1923,25 @@
       <c r="D13" s="10"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="55" t="str">
+      <c r="G13" s="46"/>
+      <c r="H13" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I13" s="46"/>
+      <c r="I13" s="42"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="42"/>
+      <c r="M13" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="N13" s="10"/>
       <c r="O13" s="12"/>
-      <c r="P13" s="42"/>
+      <c r="P13" s="38"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="12"/>
-      <c r="S13" s="56"/>
+      <c r="S13" s="49"/>
       <c r="T13"/>
     </row>
     <row r="14" spans="3:20" x14ac:dyDescent="0.3">
@@ -1977,22 +1951,25 @@
       <c r="D14" s="10"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="55" t="str">
+      <c r="G14" s="46"/>
+      <c r="H14" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I14" s="46"/>
+      <c r="I14" s="42"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="12"/>
-      <c r="M14" s="42"/>
+      <c r="M14" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="N14" s="10"/>
       <c r="O14" s="12"/>
-      <c r="P14" s="42"/>
+      <c r="P14" s="38"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="12"/>
-      <c r="S14" s="56"/>
+      <c r="S14" s="49"/>
       <c r="T14"/>
     </row>
     <row r="15" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2002,135 +1979,138 @@
       <c r="D15" s="13"/>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="62" t="str">
+      <c r="G15" s="47"/>
+      <c r="H15" s="55" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I15" s="47"/>
+      <c r="I15" s="43"/>
       <c r="J15" s="14"/>
       <c r="K15" s="14"/>
       <c r="L15" s="15"/>
-      <c r="M15" s="43"/>
+      <c r="M15" s="55" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="N15" s="13"/>
       <c r="O15" s="15"/>
-      <c r="P15" s="43"/>
+      <c r="P15" s="39"/>
       <c r="Q15" s="13"/>
       <c r="R15" s="15"/>
-      <c r="S15" s="57"/>
+      <c r="S15" s="50"/>
       <c r="T15"/>
     </row>
     <row r="16" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D16" s="76"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="76"/>
-      <c r="N16" s="76"/>
-      <c r="P16" s="78"/>
-      <c r="S16" s="78"/>
+      <c r="D16" s="65"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="65"/>
+      <c r="N16" s="65"/>
+      <c r="P16" s="67"/>
+      <c r="S16" s="67"/>
     </row>
     <row r="17" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="22">
         <v>8</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="23">
         <v>7</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="23">
         <v>8</v>
       </c>
-      <c r="G17" s="59">
+      <c r="G17" s="52">
         <v>7</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="21">
         <v>30</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="22">
         <v>6</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="23">
         <v>9</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="23">
         <v>8</v>
       </c>
-      <c r="L17" s="59">
+      <c r="L17" s="52">
         <v>7</v>
       </c>
-      <c r="M17" s="23">
+      <c r="M17" s="21">
         <v>30</v>
       </c>
-      <c r="N17" s="24">
+      <c r="N17" s="22">
         <v>60</v>
       </c>
-      <c r="O17" s="59">
+      <c r="O17" s="52">
         <v>40</v>
       </c>
-      <c r="P17" s="23">
+      <c r="P17" s="21">
         <v>30</v>
       </c>
-      <c r="Q17" s="24">
+      <c r="Q17" s="22">
         <v>52</v>
       </c>
-      <c r="R17" s="26">
+      <c r="R17" s="24">
         <v>32</v>
       </c>
-      <c r="S17" s="58">
+      <c r="S17" s="51">
         <v>30</v>
       </c>
       <c r="T17"/>
     </row>
     <row r="18" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C18" s="20"/>
-      <c r="D18" s="77"/>
+      <c r="D18" s="66"/>
       <c r="E18" s="20"/>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="66"/>
       <c r="J18" s="20"/>
       <c r="K18" s="20"/>
       <c r="L18" s="20"/>
-      <c r="M18" s="89"/>
-      <c r="N18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="N18" s="66"/>
       <c r="O18" s="20"/>
-      <c r="P18" s="89"/>
-      <c r="Q18" s="27" t="s">
+      <c r="P18" s="77"/>
+      <c r="Q18" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="R18" s="28"/>
-      <c r="S18" s="81"/>
+      <c r="R18" s="85"/>
+      <c r="S18"/>
     </row>
     <row r="19" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D19" s="79"/>
-      <c r="H19" s="78"/>
-      <c r="N19" s="79"/>
-      <c r="P19" s="78"/>
-      <c r="S19" s="78"/>
+      <c r="D19" s="68"/>
+      <c r="H19" s="67"/>
+      <c r="N19" s="68"/>
+      <c r="P19" s="67"/>
+      <c r="S19" s="67"/>
     </row>
     <row r="20" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D20" s="48" t="s">
+      <c r="D20" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="48" t="s">
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="71"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="O20" s="49"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="83"/>
-      <c r="R20" s="83"/>
-      <c r="S20" s="92"/>
+      <c r="O20" s="87"/>
+      <c r="P20" s="88"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="71"/>
+      <c r="S20" s="80"/>
     </row>
     <row r="21" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D21" s="4" t="s">
@@ -2148,7 +2128,7 @@
       <c r="H21" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I21" s="81"/>
+      <c r="I21"/>
       <c r="N21" s="4" t="s">
         <v>4</v>
       </c>
@@ -2159,537 +2139,497 @@
         <v>13</v>
       </c>
       <c r="Q21"/>
-      <c r="S21" s="78"/>
+      <c r="S21" s="67"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C22" s="1">
         <v>1</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="26">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="27">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="27">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="28">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="H22" s="63">
+      <c r="H22" s="56">
         <f>IF(COUNTBLANK(D22:G22)&gt;0,"",SUM(D22:G22))</f>
         <v>4.5138888888888888E-2</v>
       </c>
-      <c r="I22" s="81"/>
-      <c r="N22" s="30">
+      <c r="I22"/>
+      <c r="N22" s="26">
         <v>3.4722222222222224E-2</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="28">
         <v>1.7361111111111112E-2</v>
       </c>
-      <c r="P22" s="63">
+      <c r="P22" s="56">
         <f>IF(COUNTBLANK(N22:O22)&gt;0,"",SUM(N22:O22))</f>
         <v>5.2083333333333336E-2</v>
       </c>
       <c r="Q22"/>
-      <c r="S22" s="78"/>
+      <c r="S22" s="67"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C23" s="2">
         <v>2</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="29">
         <v>5.8333333333333336E-3</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="30">
         <v>1.1921296296296296E-2</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="30">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="31">
         <v>9.6527777777777775E-3</v>
       </c>
-      <c r="H23" s="63">
-        <f t="shared" ref="H23:H32" si="1">IF(COUNTBLANK(D23:G23)&gt;0,"",SUM(D23:G23))</f>
+      <c r="H23" s="56">
+        <f t="shared" ref="H23:H32" si="2">IF(COUNTBLANK(D23:G23)&gt;0,"",SUM(D23:G23))</f>
         <v>4.1296296296296289E-2</v>
       </c>
-      <c r="I23" s="81"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="63" t="str">
+      <c r="I23"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="56" t="str">
         <f>IF(COUNTBLANK(N23:O23)&gt;0,"",SUM(N23:O23))</f>
         <v/>
       </c>
       <c r="Q23"/>
-      <c r="S23" s="78"/>
+      <c r="S23" s="67"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C24" s="2">
         <v>3</v>
       </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="63" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I24" s="81"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="63" t="str">
-        <f t="shared" ref="P23:P32" si="2">IF(COUNTBLANK(N24:O24)&gt;0,"",SUM(N24:O24))</f>
+      <c r="D24" s="29"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="56" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I24"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="56" t="str">
+        <f t="shared" ref="P24:P32" si="3">IF(COUNTBLANK(N24:O24)&gt;0,"",SUM(N24:O24))</f>
         <v/>
       </c>
       <c r="Q24"/>
-      <c r="S24" s="78"/>
+      <c r="S24" s="67"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C25" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="63" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I25" s="81"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="63" t="str">
+      <c r="D25" s="29"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="56" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="I25"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="Q25"/>
-      <c r="S25" s="78"/>
+      <c r="S25" s="67"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C26" s="2">
         <v>5</v>
       </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="63" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I26" s="81"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="63" t="str">
+      <c r="D26" s="29"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="56" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="I26"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="Q26"/>
-      <c r="S26" s="78"/>
+      <c r="S26" s="67"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C27" s="2">
         <v>6</v>
       </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="63" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I27" s="81"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="81"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="63" t="str">
+      <c r="D27" s="29"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="56" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="I27"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="Q27"/>
-      <c r="S27" s="78"/>
+      <c r="S27" s="67"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C28" s="2">
         <v>7</v>
       </c>
-      <c r="D28" s="33"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="63" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I28" s="81"/>
-      <c r="K28" s="81"/>
-      <c r="L28" s="81"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="63" t="str">
+      <c r="D28" s="29"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="56" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="I28"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="Q28"/>
-      <c r="S28" s="78"/>
+      <c r="S28" s="67"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C29" s="2">
         <v>8</v>
       </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="63" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I29" s="81"/>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="63" t="str">
+      <c r="D29" s="29"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="56" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="I29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="Q29"/>
-      <c r="S29" s="78"/>
+      <c r="S29" s="67"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C30" s="2">
         <v>9</v>
       </c>
-      <c r="D30" s="33"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="63" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I30" s="81"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="63" t="str">
+      <c r="D30" s="29"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="56" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="I30"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="Q30"/>
-      <c r="S30" s="78"/>
+      <c r="S30" s="67"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C31" s="2">
         <v>10</v>
       </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="63" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I31" s="81"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="63" t="str">
+      <c r="D31" s="29"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="56" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="I31"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="Q31"/>
-      <c r="S31" s="78"/>
+      <c r="S31" s="67"/>
     </row>
     <row r="32" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="3">
         <v>11</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="64" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I32" s="84"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="91"/>
-      <c r="N32" s="36"/>
-      <c r="O32" s="38"/>
-      <c r="P32" s="64" t="str">
+      <c r="D32" s="32"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="57" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="I32" s="72"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="Q32"/>
-      <c r="S32" s="78"/>
+      <c r="S32" s="67"/>
     </row>
     <row r="33" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D33" s="76"/>
-      <c r="H33" s="78"/>
-      <c r="N33" s="76"/>
-      <c r="P33" s="78"/>
-      <c r="Q33" s="86"/>
-      <c r="R33" s="83"/>
-      <c r="S33" s="92"/>
+      <c r="D33" s="65"/>
+      <c r="H33" s="67"/>
+      <c r="N33" s="65"/>
+      <c r="P33" s="67"/>
+      <c r="Q33" s="74"/>
+      <c r="R33" s="71"/>
+      <c r="S33" s="80"/>
     </row>
     <row r="34" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="39">
+      <c r="D34" s="35">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="E34" s="40">
+      <c r="E34" s="36">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="F34" s="40">
+      <c r="F34" s="36">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="G34" s="60">
+      <c r="G34" s="53">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="H34" s="75">
+      <c r="H34" s="89">
         <v>4.5138888888888888E-2</v>
       </c>
-      <c r="I34" s="87"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="87"/>
-      <c r="N34" s="72">
+      <c r="I34" s="76"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="76"/>
+      <c r="L34" s="76"/>
+      <c r="M34" s="75"/>
+      <c r="N34" s="62">
         <v>3.4722222222222224E-2</v>
       </c>
-      <c r="O34" s="41">
+      <c r="O34" s="37">
         <v>1.7361111111111112E-2</v>
       </c>
-      <c r="P34" s="61">
+      <c r="P34" s="54">
         <v>5.2083333333333336E-2</v>
       </c>
-      <c r="Q34" s="88"/>
-      <c r="R34" s="88"/>
-      <c r="S34" s="87"/>
+      <c r="Q34" s="76"/>
+      <c r="R34" s="76"/>
+      <c r="S34" s="75"/>
     </row>
     <row r="35" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="D35" s="80"/>
-      <c r="H35" s="78"/>
-      <c r="N35" s="80"/>
-      <c r="P35" s="78"/>
-      <c r="S35" s="78"/>
+      <c r="D35" s="69"/>
+      <c r="H35" s="67"/>
+      <c r="N35" s="69"/>
+      <c r="P35" s="67"/>
+      <c r="S35" s="67"/>
     </row>
     <row r="36" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D36" s="79"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="79"/>
-      <c r="N36" s="79"/>
-      <c r="P36" s="78"/>
-      <c r="S36" s="78"/>
+      <c r="D36" s="68"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="68"/>
+      <c r="N36" s="68"/>
+      <c r="P36" s="67"/>
+      <c r="S36" s="67"/>
     </row>
     <row r="37" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C37" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="92">
         <f>IFERROR(AVERAGE(D5:D15),"")</f>
         <v>5.5</v>
       </c>
-      <c r="E37" s="17">
-        <f t="shared" ref="E37:S37" si="3">IFERROR(AVERAGE(E5:E15),"")</f>
+      <c r="E37" s="93">
+        <f t="shared" ref="E37:S37" si="4">IFERROR(AVERAGE(E5:E15),"")</f>
         <v>5</v>
       </c>
-      <c r="F37" s="17">
-        <f t="shared" si="3"/>
+      <c r="F37" s="93">
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="G37" s="65">
-        <f t="shared" si="3"/>
+      <c r="G37" s="94">
+        <f t="shared" si="4"/>
         <v>5.5</v>
       </c>
-      <c r="H37" s="67">
-        <f t="shared" si="3"/>
+      <c r="H37" s="60">
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="I37" s="66">
-        <f t="shared" si="3"/>
+      <c r="I37" s="59">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="J37" s="17">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f t="shared" si="4"/>
+        <v>6.5</v>
       </c>
       <c r="K37" s="17">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="L37" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>6.5</v>
+      </c>
+      <c r="L37" s="58">
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="M37" s="67">
-        <f t="shared" si="3"/>
-        <v>26</v>
-      </c>
-      <c r="N37" s="66">
-        <f t="shared" si="3"/>
-        <v>41</v>
-      </c>
-      <c r="O37" s="65">
-        <f t="shared" si="3"/>
+      <c r="M37" s="60">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="N37" s="59">
+        <f t="shared" si="4"/>
+        <v>39.5</v>
+      </c>
+      <c r="O37" s="58">
+        <f t="shared" si="4"/>
         <v>27.5</v>
       </c>
-      <c r="P37" s="67">
-        <f t="shared" si="3"/>
+      <c r="P37" s="60">
+        <f t="shared" si="4"/>
         <v>68.5</v>
       </c>
-      <c r="Q37" s="66" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q37" s="59" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R37" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="S37" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="S37" s="60" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T37"/>
     </row>
     <row r="38" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="D38" s="68">
+      <c r="D38" s="63">
         <f>IFERROR(AVERAGE(D22:D32),"")</f>
         <v>6.3888888888888884E-3</v>
       </c>
-      <c r="E38" s="69">
-        <f t="shared" ref="E38:K38" si="4">IFERROR(AVERAGE(E22:E32),"")</f>
+      <c r="E38" s="95">
+        <f t="shared" ref="E38:H38" si="5">IFERROR(AVERAGE(E22:E32),"")</f>
         <v>1.2905092592592593E-2</v>
       </c>
-      <c r="F38" s="70">
-        <f t="shared" si="4"/>
+      <c r="F38" s="95">
+        <f t="shared" si="5"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="G38" s="71">
-        <f t="shared" si="4"/>
+      <c r="G38" s="64">
+        <f t="shared" si="5"/>
         <v>1.0034722222222223E-2</v>
       </c>
-      <c r="H38" s="71">
-        <f t="shared" si="4"/>
+      <c r="H38" s="91">
+        <f t="shared" si="5"/>
         <v>4.3217592592592585E-2</v>
       </c>
       <c r="I38"/>
       <c r="L38" s="19"/>
-      <c r="M38" s="94"/>
-      <c r="N38" s="73">
+      <c r="M38" s="82"/>
+      <c r="N38" s="63">
         <f>IFERROR(AVERAGE(N22:N32),"")</f>
         <v>3.4722222222222224E-2</v>
       </c>
-      <c r="O38" s="74">
+      <c r="O38" s="64">
         <f>IFERROR(AVERAGE(O22:O32),"")</f>
         <v>1.7361111111111112E-2</v>
       </c>
-      <c r="P38" s="71">
+      <c r="P38" s="61">
         <f>IFERROR(AVERAGE(P22:P32),"")</f>
         <v>5.2083333333333336E-2</v>
       </c>
       <c r="Q38"/>
-      <c r="S38" s="95"/>
+      <c r="S38" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="N20:P20"/>
     <mergeCell ref="Q18:R18"/>
     <mergeCell ref="D3:H3"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="I3:M3"/>
     <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="N20:P20"/>
   </mergeCells>
-  <conditionalFormatting sqref="D22:H32 D38:H38 N22:P32">
-    <cfRule type="expression" dxfId="23" priority="35">
+  <conditionalFormatting sqref="D22:H32 N22:P32 D38:H38">
+    <cfRule type="expression" dxfId="13" priority="35">
       <formula>AND(ISNUMBER(D22),D22&lt;=D$34)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="36">
+    <cfRule type="expression" dxfId="12" priority="36">
       <formula>AND(ISNUMBER(D22),D22&gt;D$34)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:R15">
-    <cfRule type="expression" dxfId="21" priority="37">
+  <conditionalFormatting sqref="D5:S15">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&lt;=20%)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="38">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&gt;20%,D5/D$17&lt;=40%)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="39">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&gt;40%,D5/D$17&lt;=60%)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="40">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&gt;60%,D5/D$17&lt;=80%)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="41">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>AND(ISNUMBER(D5),D$17&gt;0,D5/D$17&gt;80%)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37:S37">
-    <cfRule type="expression" dxfId="16" priority="42">
+    <cfRule type="expression" dxfId="6" priority="42">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&lt;=20%)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="43">
+    <cfRule type="expression" dxfId="5" priority="43">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&gt;20%,D37/D$17&lt;=40%)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="44">
+    <cfRule type="expression" dxfId="4" priority="44">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&gt;40%,D37/D$17&lt;=60%)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="45">
+    <cfRule type="expression" dxfId="3" priority="45">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&gt;60%,D37/D$17&lt;=80%)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="46">
+    <cfRule type="expression" dxfId="2" priority="46">
       <formula>AND(ISNUMBER(D37),D$17&gt;0,D37/D$17&gt;80%)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S6:S15">
-    <cfRule type="expression" dxfId="11" priority="18">
-      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&lt;=20%)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="19">
-      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&gt;20%,S6/S$17&lt;=40%)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="20">
-      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&gt;40%,S6/S$17&lt;=60%)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="21">
-      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&gt;60%,S6/S$17&lt;=80%)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="22">
-      <formula>AND(ISNUMBER(S6),S$17&gt;0,S6/S$17&gt;80%)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5">
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&lt;=20%)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="9">
-      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&gt;20%,S5/S$17&lt;=40%)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="10">
-      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&gt;40%,S5/S$17&lt;=60%)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="11">
-      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&gt;60%,S5/S$17&lt;=80%)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="12">
-      <formula>AND(ISNUMBER(S5),S$17&gt;0,S5/S$17&gt;80%)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N38:P38">
